--- a/paper_draft/table/OccamQA prompt.xlsx
+++ b/paper_draft/table/OccamQA prompt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ker\Desktop\Document\paper\AgentOccam1\paper_draft\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3663254D-742F-4450-A89A-373002B96A03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994606F1-C9BB-405C-B3F6-7469ACC54AF1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="9276" xr2:uid="{FD044680-57D5-43AE-BA20-D7D2A459AD94}"/>
   </bookViews>
@@ -35,24 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>You are an AI assistant executing browser-based tasks and Gherkin test cases.
-When the task brief contains Gherkin sections, act as a tester.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>. GIVEN describes the initial/current state and preconditions.
-. WHEN describes the required user actions; perform them in order.
-. THEN describes the expected final result; verify it before stop.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>. Do not skip required WHEN steps.
-. Do not replace step execution with a vague goal.
-. Do not stop before THEN expectations are checked.
-. When stopping, report evidence proving the expected outcome.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gherkin semantics prompt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -61,11 +43,33 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>. objective: current task goal and test requirements
-. previous plans: prior high-level planning context
-. interaction history: executed actions and page reactions
-. current observation: textual page-state description
-. current visual observation: screenshot-based visual context</t>
+    <t>. GIVEN describes the I8initial/current state and preconditions. Use it as context to confirm where you are and what should already be true.
+. WHEN describes the required user actions. Perform these actions in order, using equivalent UI interactions only when necessary.
+. THEN describes the expected final result, screen, message, data, or state. Verify these expectations from the page before using `stop`.
+. Do not optimize toward a vague goal if that would skip a WHEN step or stop before the THEN assertions are checked.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>. GHERKIN TASK section
+. current step
+. web page observations
+. previous plans
+. interaction history
+. current visual observation (optional multimodal input)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You are an AI assistant executing browser-based tasks and Gherkin test cases. You will be provided with the GHERKIN TASK section, current step, web page observations, previous plans, and interaction history. You need to issue an action for this step.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generate the response in the required format.
+Only one single action can be issued at a time.
+Available action types:
+- planning actions: branch, prune
+- navigation actions: click, type, stop, note, go_back
+For Gherkin tasks, `stop [answer]` should include the key information
+that verifies the acceptance criteria from the THEN clauses.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -569,52 +573,52 @@
     <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" s="5" customFormat="1" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" s="5" customFormat="1" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
       <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:7" s="9" customFormat="1" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="9" customFormat="1" ht="145.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="13" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="4" spans="1:7" s="7" customFormat="1" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" s="7" customFormat="1" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="15" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A5" s="16"/>
       <c r="B5" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>

--- a/paper_draft/table/OccamQA prompt.xlsx
+++ b/paper_draft/table/OccamQA prompt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ker\Desktop\Document\paper\AgentOccam1\paper_draft\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994606F1-C9BB-405C-B3F6-7469ACC54AF1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E35D0C2-E9AD-4413-A8DF-88FC94E22908}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="9276" xr2:uid="{FD044680-57D5-43AE-BA20-D7D2A459AD94}"/>
   </bookViews>
@@ -43,13 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>. GIVEN describes the I8initial/current state and preconditions. Use it as context to confirm where you are and what should already be true.
-. WHEN describes the required user actions. Perform these actions in order, using equivalent UI interactions only when necessary.
-. THEN describes the expected final result, screen, message, data, or state. Verify these expectations from the page before using `stop`.
-. Do not optimize toward a vague goal if that would skip a WHEN step or stop before the THEN assertions are checked.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>. GHERKIN TASK section
 . current step
 . web page observations
@@ -70,6 +63,13 @@
 - navigation actions: click, type, stop, note, go_back
 For Gherkin tasks, `stop [answer]` should include the key information
 that verifies the acceptance criteria from the THEN clauses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>. GIVEN describes the Initial/current state and preconditions. Use it as context to confirm where you are and what should already be true.
+. WHEN describes the required user actions. Perform these actions in order, using equivalent UI interactions only when necessary.
+. THEN describes the expected final result, screen, message, data, or state. Verify these expectations from the page before using `stop`.
+. Do not optimize toward a vague goal if that would skip a WHEN step or stop before the THEN assertions are checked.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -592,7 +592,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="18"/>
@@ -605,7 +605,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
